--- a/docs/downloads/04/tbl_raisons_non_scol_marovoay_bepako.xlsx
+++ b/docs/downloads/04/tbl_raisons_non_scol_marovoay_bepako.xlsx
@@ -423,12 +423,6 @@
           <t>Autre</t>
         </is>
       </c>
-      <c r="C4">
-        <v>2</v>
-      </c>
-      <c r="D4">
-        <v>1.7</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -459,12 +453,6 @@
           <t>Besoin revenu</t>
         </is>
       </c>
-      <c r="C6">
-        <v>2</v>
-      </c>
-      <c r="D6">
-        <v>1.7</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -495,12 +483,6 @@
           <t>Handicap / maladie</t>
         </is>
       </c>
-      <c r="C8">
-        <v>1</v>
-      </c>
-      <c r="D8">
-        <v>0.8</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -513,12 +495,6 @@
           <t>Main-d'oeuvre exploitation</t>
         </is>
       </c>
-      <c r="C9">
-        <v>4</v>
-      </c>
-      <c r="D9">
-        <v>3.3</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -566,12 +542,6 @@
         <is>
           <t>École trop éloignée</t>
         </is>
-      </c>
-      <c r="C12">
-        <v>1</v>
-      </c>
-      <c r="D12">
-        <v>0.8</v>
       </c>
     </row>
   </sheetData>
